--- a/data/아실_매교역팰루시드_전체매물_20261003.xlsx
+++ b/data/아실_매교역팰루시드_전체매물_20261003.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA63"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42753202</t>
+          <t>42800059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -579,22 +579,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>118동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -643,29 +643,25 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O안전한거래는이강O현금전세,에어컨4,입주일협의</t>
+          <t>O냉장고풀셋,에어컨풀O전월세매물많은집사전점검함께해요</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>50000</v>
+        <v>48000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -679,12 +675,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42752520</t>
+          <t>42798115</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -694,32 +690,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -729,7 +725,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -739,17 +735,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -758,17 +754,13 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
@@ -777,17 +769,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O전월세는이강O귀한101타입,채광굿,입주일협의가능</t>
         </is>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -798,12 +790,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42764006</t>
+          <t>42798105</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -813,12 +805,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -833,12 +825,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -848,7 +840,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -858,17 +850,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -877,7 +869,11 @@
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -885,24 +881,20 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,워시타워</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
@@ -913,12 +905,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42750885</t>
+          <t>42798092</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -928,7 +920,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -948,12 +940,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -963,27 +955,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>115,272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -992,11 +984,7 @@
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -1004,20 +992,24 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O정상거래O당일확인,에어컨4,붙박이장,인덕션</t>
+          <t>O이강에서집봐요O층높아채광굿,조합원세대,옵션굿</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>115272</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -1033,7 +1025,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42764005</t>
+          <t>42753202</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1043,7 +1035,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>118동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1063,12 +1055,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1088,7 +1080,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1107,25 +1099,29 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O안전한거래는이강O현금전세,에어컨4,입주일협의</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>53000</v>
+        <v>50000</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1144,7 +1140,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42748884</t>
+          <t>42752520</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1154,32 +1150,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1224,12 +1220,12 @@
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1237,14 +1233,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O와이드주방O현금전세,중문,에어컨4,정원뷰예뻐요</t>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>53000</v>
+        <v>50000</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1263,7 +1259,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42748771</t>
+          <t>42764006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1273,32 +1269,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1318,7 +1314,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1338,13 +1334,13 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1352,14 +1348,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O이강에서집봐요O빠른입주협의가능,채광좋아요</t>
+          <t>O채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>53000</v>
+        <v>45000</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1373,12 +1369,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42748104</t>
+          <t>42750885</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1388,7 +1384,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1408,12 +1404,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1423,17 +1419,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,272</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1452,29 +1448,29 @@
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
+          <t>O정상거래O당일확인,에어컨4,붙박이장,인덕션</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>115272</v>
       </c>
       <c r="Z9" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1493,7 +1489,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>42748095</t>
+          <t>42764005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1503,7 +1499,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1523,12 +1519,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1543,12 +1539,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1567,11 +1563,7 @@
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1582,14 +1574,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1603,12 +1595,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>42747678</t>
+          <t>42748884</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1618,32 +1610,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1653,7 +1645,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1663,12 +1655,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1682,10 +1674,18 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>O</t>
@@ -1693,17 +1693,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
+          <t>O와이드주방O현금전세,중문,에어컨4,정원뷰예뻐요</t>
         </is>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>30000</v>
+        <v>53000</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42747591</t>
+          <t>42748771</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>117동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1793,33 +1793,29 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O대출XO현금전세,에어컨4,욕실팬,중문,붙박이장</t>
+          <t>O이강에서집봐요O빠른입주협의가능,채광좋아요</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1838,7 +1834,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>42747431</t>
+          <t>42748104</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1848,7 +1844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>103동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1868,12 +1864,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1912,25 +1908,29 @@
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
+          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42747413</t>
+          <t>42748095</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1959,32 +1959,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2023,25 +2023,29 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O가전제품FULL.입주일협의</t>
+          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z14" t="n">
-        <v>48000</v>
+        <v>52000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2055,12 +2059,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42747093</t>
+          <t>42747678</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2070,32 +2074,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>123동</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2115,12 +2119,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2134,32 +2138,28 @@
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
         </is>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>42747591</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2185,32 +2185,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2249,29 +2249,33 @@
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
+          <t>O대출XO현금전세,에어컨4,욕실팬,중문,붙박이장</t>
         </is>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>47000</v>
+        <v>50000</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42747038</t>
+          <t>42747431</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2300,32 +2304,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>103동</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2364,25 +2368,25 @@
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>O냉장고풀셋,에어컨풀O전월세매물많은집사전점검함께해요</t>
+          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2396,12 +2400,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42746992</t>
+          <t>42747413</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2411,32 +2415,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2446,17 +2450,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2481,27 +2485,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>O피2.5억O뻥뷰,중도금대출승계가능,입주기간지나고대출가능</t>
+          <t>O조건맞춰드립니다O가전제품FULL.입주일협의</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2520,7 +2516,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42746979</t>
+          <t>42747093</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2530,32 +2526,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2575,7 +2571,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2594,33 +2590,29 @@
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>O전세대출가능,트인조망O채광좋은라인,입주일협의가능</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2639,7 +2631,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42746931</t>
+          <t>42747074</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2649,32 +2641,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2694,7 +2686,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2719,23 +2711,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
+          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
         </is>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>70000</v>
+        <v>47000</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2749,12 +2741,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42704440</t>
+          <t>42746992</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2764,7 +2756,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2784,32 +2776,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2819,7 +2811,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2828,29 +2820,33 @@
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
+          <t>O피2.5억O뻥뷰,중도금대출승계가능,입주기간지나고대출가능</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z21" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2864,12 +2860,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>42704438</t>
+          <t>42746979</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2879,42 +2875,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>125동</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2924,17 +2920,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2949,22 +2945,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
+          <t>O전세대출가능,트인조망O채광좋은라인,입주일협의가능</t>
         </is>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>10000</v>
+        <v>48000</v>
       </c>
       <c r="AA22" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>42703982</t>
+          <t>42746931</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2990,32 +2994,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3035,7 +3039,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3045,7 +3049,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3054,11 +3058,7 @@
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>O</t>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
+          <t>O전세는이강O귀한101타입,채광굿,입주일협의가능</t>
         </is>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>45000</v>
+        <v>70000</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>42698784</t>
+          <t>42704440</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3109,37 +3109,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>125동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3185,21 +3185,17 @@
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>O뻥뷰O대출가능,채광좋은남동향,에어컨4,인덕션등</t>
+          <t>O조건맞춰드립니다O전세대출가능,반전세가능,시스템풀</t>
         </is>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3213,12 +3209,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>42664558</t>
+          <t>42704438</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3228,42 +3224,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>120동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3273,17 +3269,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3293,23 +3289,27 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>O저렴전세O이강에서집봐요,조건맞춰드립니다</t>
+          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
         </is>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>42664173</t>
+          <t>42703982</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3335,32 +3335,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3370,17 +3370,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>115,030</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3399,8 +3399,16 @@
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
@@ -3410,14 +3418,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
+          <t>O조건맞춰드립니다O채광좋은남동향,시에4,입주협의</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>115030</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3431,12 +3439,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42615752</t>
+          <t>42698784</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3446,42 +3454,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>115동</t>
+          <t>125동</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3491,17 +3499,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3510,28 +3518,36 @@
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>O전입XO보증금1억가능,빠른입주환영,역가까운로얄동</t>
+          <t>O뻥뷰O대출가능,채광좋은남동향,에어컨4,인덕션등</t>
         </is>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="AA27" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3542,12 +3558,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>42615708</t>
+          <t>42664558</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3557,32 +3573,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>120동</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3592,17 +3608,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>114,530</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3612,7 +3628,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3621,29 +3637,21 @@
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
+          <t>O저렴전세O이강에서집봐요,조건맞춰드립니다</t>
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>114530</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3657,12 +3665,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>42600581</t>
+          <t>42664173</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3672,32 +3680,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3707,17 +3715,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115,030</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3727,7 +3735,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3736,33 +3744,25 @@
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
+          <t>OP2.3억O당일확인,귀한트인조망,채광환기굿</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>115030</v>
       </c>
       <c r="Z29" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42600586</t>
+          <t>42615752</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3791,42 +3791,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130동</t>
+          <t>115동</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>42,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3866,17 +3866,17 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>O빠른입주환영O이강에서집봐요,역가까운인기동</t>
+          <t>O전입XO보증금1억가능,빠른입주환영,역가까운로얄동</t>
         </is>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>42000</v>
+        <v>5000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42600580</t>
+          <t>42615708</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3902,32 +3902,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3937,17 +3937,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114,530</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3966,29 +3966,29 @@
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>O전세대출가능,융자없음.귀한고층매물탁트인뷰,인기동</t>
+          <t>O피2.5억O셔세권동,필로티2층,시에4.중문</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>114530</v>
       </c>
       <c r="Z31" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>42559005</t>
+          <t>42600581</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4017,32 +4017,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4081,32 +4081,36 @@
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>O이강에서집봐요O층높아채광굿,조합원세대,옵션굿</t>
+          <t>O대출가능O융자없음.가전원옵션풀,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4122,7 +4126,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42558979</t>
+          <t>42600586</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4132,37 +4136,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>128동</t>
+          <t>130동</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4177,7 +4181,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>42,000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4204,21 +4208,17 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>O71타입로얄동O채광굿,입주협의가능</t>
+          <t>O빠른입주환영O이강에서집봐요,역가까운인기동</t>
         </is>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>55000</v>
+        <v>42000</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42600579</t>
+          <t>42600580</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4247,32 +4247,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>123동</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4313,7 +4313,11 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
@@ -4322,14 +4326,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
+          <t>O전세대출가능,융자없음.귀한고층매물탁트인뷰,인기동</t>
         </is>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>53000</v>
+        <v>50000</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4343,12 +4347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>42557757</t>
+          <t>42558979</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4358,42 +4362,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>128동</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4403,12 +4407,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4430,20 +4434,24 @@
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>O인기동,전입가능O조건맞춰찾아드립니다입주일협의</t>
+          <t>O71타입로얄동O채광굿,입주협의가능</t>
         </is>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="AA35" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4454,12 +4462,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>42556700</t>
+          <t>42600579</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4469,7 +4477,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4489,12 +4497,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4504,7 +4512,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4514,12 +4522,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4533,28 +4541,28 @@
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>O전입불가O시스템에어컨4,초등학교가까운동</t>
+          <t>O조건맞춰드립니다O현금전세,따뜻한단지내뷰,융무</t>
         </is>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4000</v>
+        <v>53000</v>
       </c>
       <c r="AA36" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4565,12 +4573,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>42554817</t>
+          <t>42557757</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4580,32 +4588,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4615,22 +4623,22 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>매매</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>119,720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4644,32 +4652,28 @@
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨5대무상</t>
+          <t>O인기동,전입가능O조건맞춰찾아드립니다입주일협의</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>119720</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38">
@@ -4680,12 +4684,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>42600578</t>
+          <t>42556700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4695,7 +4699,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4715,12 +4719,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4730,7 +4734,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4740,12 +4744,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4764,27 +4768,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O시스템에어컨4대,입주협의</t>
+          <t>O전입불가O시스템에어컨4,초등학교가까운동</t>
         </is>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>55000</v>
+        <v>4000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>42490332</t>
+          <t>42554817</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>119,372</t>
+          <t>119,720</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4874,14 +4874,14 @@
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>O</t>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>O피500O로얄동,붙박이장,따뜻한단지조경뷰</t>
+          <t>O정원뷰O2층커뮤니티동귀한대형평형시스템에어컨5대무상</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>119372</v>
+        <v>119720</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>42490328</t>
+          <t>42600578</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5000,22 +5000,18 @@
         </is>
       </c>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
-          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
+          <t>O조건맞춰드립니다O시스템에어컨4대,입주협의</t>
         </is>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5029,12 +5025,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>42490321</t>
+          <t>42490332</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5044,32 +5040,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5079,17 +5075,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>매매</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119,372</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>57,000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5109,32 +5105,28 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
+          <t>O피500O로얄동,붙박이장,따뜻한단지조경뷰</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>119372</v>
       </c>
       <c r="Z41" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5153,7 +5145,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>42490304</t>
+          <t>42490328</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5163,7 +5155,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>111동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5183,12 +5175,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5237,16 +5229,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
-          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
+          <t>O늦은입주OKO시에4,실링팬,중문,입주청소,예쁜집</t>
         </is>
       </c>
       <c r="Y42" t="n">
@@ -5272,7 +5264,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>42490045</t>
+          <t>42490321</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5282,7 +5274,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>117동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5302,14 +5294,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>15</t>
@@ -5327,7 +5319,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>57,000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -5347,7 +5339,11 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>O</t>
@@ -5361,14 +5357,14 @@
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
+          <t>O전세대출가능O입주청소,줄눈,탄성코팅,냉장고3대,인덕션등</t>
         </is>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -5387,7 +5383,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>42489874</t>
+          <t>42490304</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5397,7 +5393,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>111동</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5417,12 +5413,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5442,7 +5438,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -5461,21 +5457,33 @@
         </is>
       </c>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>O조건맞춰찾아드립니다O이강에서집봐요,통근버스가까운동</t>
+          <t>O전세대출가능O융자없음,인덕션,시스템에어컨4,입주협의</t>
         </is>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -5494,7 +5502,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>42489832</t>
+          <t>42490045</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5504,7 +5512,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5524,12 +5532,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5549,7 +5557,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5568,29 +5576,29 @@
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
-          <t>O시스템에어컨4O입주일협의,초등학교가까운동</t>
+          <t>O매물답사가능O전세대출가능,냉장고,냉동,김냉,인덕션등</t>
         </is>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -5604,12 +5612,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>42527493</t>
+          <t>42489874</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5619,32 +5627,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5654,7 +5662,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5664,12 +5672,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5685,34 +5693,22 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O조건맞춰찾아드립니다O이강에서집봐요,통근버스가까운동</t>
         </is>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>25000</v>
+        <v>55000</v>
       </c>
       <c r="AA46" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5728,7 +5724,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>42441234</t>
+          <t>42489832</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5738,7 +5734,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5758,12 +5754,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5783,7 +5779,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5793,7 +5789,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -5802,7 +5798,11 @@
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>O</t>
@@ -5813,14 +5813,14 @@
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
+          <t>O시스템에어컨4O입주일협의,초등학교가까운동</t>
         </is>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>42383838</t>
+          <t>42527493</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5849,32 +5849,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>108동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -5913,32 +5913,36 @@
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>O전입가능O풀옵션,시에4,냉장고,김치냉장고,워시타워등</t>
+          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="AA48" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
@@ -5949,12 +5953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>42352823</t>
+          <t>42441234</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5964,32 +5968,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5999,7 +6003,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6009,17 +6013,17 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -6028,36 +6032,28 @@
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
-          <t>O대출가능전입가능O가전옵션풀,시스템에어컨,장기거주환영</t>
+          <t>O조건맞춰드립니다O커뮤니티코앞,동간격넓은동,입주일협의가능</t>
         </is>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="AA49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6068,12 +6064,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>42242449</t>
+          <t>42383838</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6083,7 +6079,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>112동</t>
+          <t>108동</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6103,12 +6099,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6118,7 +6114,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>전세</t>
+          <t>월세</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6128,17 +6124,17 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -6147,28 +6143,32 @@
         </is>
       </c>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O현금전세,빠른입주환영,층간소음걱정없는1층</t>
+          <t>O전입가능O풀옵션,시에4,냉장고,김치냉장고,워시타워등</t>
         </is>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>60000</v>
+        <v>15000</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>42232723</t>
+          <t>42242449</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>112동</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6229,22 +6229,22 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6258,11 +6258,7 @@
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
           <t>O</t>
@@ -6270,24 +6266,20 @@
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
-          <t>O전입불가O입주일협의가능,막힘없이트인뷰,시에4</t>
+          <t>O조건맞춰드립니다O현금전세,빠른입주환영,층간소음걱정없는1층</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>5000</v>
+        <v>60000</v>
       </c>
       <c r="AA51" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6303,7 +6295,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>42142455</t>
+          <t>42232723</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6313,32 +6305,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6353,22 +6345,22 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -6382,27 +6374,31 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,워시타워</t>
+          <t>O전입불가O입주일협의가능,막힘없이트인뷰,시에4</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z52" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="AA52" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53">
@@ -7313,12 +7309,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>41926893</t>
+          <t>41951368</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7328,32 +7324,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>110동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>101.73</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7363,7 +7359,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>월세</t>
+          <t>전세</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7373,12 +7369,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7393,252 +7389,26 @@
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
-          <t>O전월세는이강O귀한101타입,채광굿,입주일협의가능</t>
+          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
         </is>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="AA61" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>41951369</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>112동</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>O조건맞춰드립니다O전입X,빠른입주환영,층간소음걱정없는1층</t>
-        </is>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>25000</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>41951368</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>102동</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>전세</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>55,000</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>O조건맞춰드립니다O대출X초등학교가까운인기동</t>
-        </is>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>55000</v>
-      </c>
-      <c r="AA63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8758,7 +8528,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42753202</t>
+          <t>42800059</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -8768,22 +8538,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>118동</t>
+          <t>129동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8813,7 +8583,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -8823,7 +8593,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -8832,29 +8602,25 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O안전한거래는이강O현금전세,에어컨4,입주일협의</t>
+          <t>O냉장고풀셋,에어컨풀O전월세매물많은집사전점검함께해요</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>50000</v>
+        <v>48000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -8873,7 +8639,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42752520</t>
+          <t>42753202</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8883,27 +8649,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>118동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -8952,21 +8718,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
+          <t>O안전한거래는이강O현금전세,에어컨4,입주일협의</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -8992,7 +8754,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42764006</t>
+          <t>42752520</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9002,32 +8764,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -9047,7 +8809,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -9066,14 +8828,18 @@
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>O</t>
@@ -9081,14 +8847,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O대출가능,전입가능O2면창채광좋은집,에어컨4대</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -9107,7 +8873,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42764005</t>
+          <t>42764006</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9117,32 +8883,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>105동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9162,7 +8928,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>53,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -9184,7 +8950,11 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>O</t>
@@ -9192,14 +8962,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
+          <t>O채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>53000</v>
+        <v>45000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -9218,7 +8988,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42748884</t>
+          <t>42764005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9228,7 +8998,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>105동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9248,12 +9018,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -9292,18 +9062,10 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>O</t>
@@ -9311,7 +9073,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O와이드주방O현금전세,중문,에어컨4,정원뷰예뻐요</t>
+          <t>O현금전세O이.강조용한단지내뷰,나무보여요</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -9337,7 +9099,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42748771</t>
+          <t>42748884</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9347,7 +9109,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9367,12 +9129,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9411,14 +9173,18 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>O</t>
@@ -9426,7 +9192,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O이강에서집봐요O빠른입주협의가능,채광좋아요</t>
+          <t>O와이드주방O현금전세,중문,에어컨4,정원뷰예뻐요</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -9452,7 +9218,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42748104</t>
+          <t>42748771</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9462,7 +9228,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9482,12 +9248,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9541,7 +9307,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
+          <t>O이강에서집봐요O빠른입주협의가능,채광좋아요</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -9567,7 +9333,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42748095</t>
+          <t>42748104</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9577,7 +9343,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9597,12 +9363,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9617,12 +9383,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -9641,12 +9407,12 @@
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
@@ -9656,14 +9422,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
+          <t>O채광좋은층O현금전세,밝고환한집,입주일협의</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -9682,7 +9448,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>42747591</t>
+          <t>42748095</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9692,7 +9458,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>117동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9712,12 +9478,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9732,12 +9498,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -9762,27 +9528,23 @@
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O대출XO현금전세,에어컨4,욕실팬,중문,붙박이장</t>
+          <t>O뻥뷰O현금전세,거실넓어요,에어컨4</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z10" t="n">
-        <v>50000</v>
+        <v>52000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -9801,7 +9563,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>42747431</t>
+          <t>42747591</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9811,7 +9573,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>103동</t>
+          <t>117동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9831,12 +9593,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9881,12 +9643,20 @@
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
+          <t>O대출XO현금전세,에어컨4,욕실팬,중문,붙박이장</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -9912,7 +9682,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42747413</t>
+          <t>42747431</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9922,32 +9692,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>122동</t>
+          <t>103동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9967,7 +9737,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9986,25 +9756,25 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O조건맞춰드립니다O가전제품FULL.입주일협의</t>
+          <t>O조건맞춰드립니다O초등학교인접인기동,시스템에어컨풀</t>
         </is>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -10023,7 +9793,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>42747093</t>
+          <t>42747413</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10033,32 +9803,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>131동</t>
+          <t>122동</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>74.16</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10078,7 +9848,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -10097,29 +9867,25 @@
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
+          <t>O조건맞춰드립니다O가전제품FULL.입주일협의</t>
         </is>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -10138,7 +9904,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42747074</t>
+          <t>42747093</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10148,32 +9914,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>129동</t>
+          <t>131동</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>74.16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>저</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10193,7 +9959,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -10212,29 +9978,29 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
+          <t>O이.강O시에3,냉장고,냉동고,김치냉장고,워시타워,인덕션</t>
         </is>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>47000</v>
+        <v>45000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -10253,7 +10019,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42747038</t>
+          <t>42747074</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10268,12 +10034,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10283,12 +10049,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>저</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -10308,7 +10074,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>47,000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -10328,24 +10094,28 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>O냉장고풀셋,에어컨풀O전월세매물많은집사전점검함께해요</t>
+          <t>O전세대출가능O입주일협의,깨끗하게입주가능해요</t>
         </is>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>48000</v>
+        <v>47000</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -13098,7 +12868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13251,7 +13021,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42747678</t>
+          <t>42798115</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -13261,32 +13031,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>110동</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101.02</t>
+          <t>129.28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>101.73</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -13311,12 +13081,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -13326,7 +13096,11 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
@@ -13336,7 +13110,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
+          <t>O전월세는이강O귀한101타입,채광굿,입주일협의가능</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -13346,7 +13120,7 @@
         <v>30000</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
@@ -13362,7 +13136,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42704438</t>
+          <t>42798105</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13372,37 +13146,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>114동</t>
+          <t>126동</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>84.42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>고</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -13417,17 +13191,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -13436,28 +13210,32 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
+          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,워시타워</t>
         </is>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA3" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -13473,7 +13251,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42615752</t>
+          <t>42798092</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13483,7 +13261,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>115동</t>
+          <t>119동</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13503,17 +13281,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -13528,17 +13306,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -13548,27 +13326,31 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>O전입XO보증금1억가능,빠른입주환영,역가까운로얄동</t>
+          <t>O이강에서집봐요O층높아채광굿,조합원세대,옵션굿</t>
         </is>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="AA4" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -13584,7 +13366,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42559005</t>
+          <t>42747678</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13594,32 +13376,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>119동</t>
+          <t>123동</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>112.60</t>
+          <t>101.02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13649,7 +13431,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -13661,11 +13443,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>O</t>
@@ -13673,7 +13451,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>O이강에서집봐요O층높아채광굿,조합원세대,옵션굿</t>
+          <t>O이강과집봐요O트인조망의어린이공원뷰</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -13699,7 +13477,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42557757</t>
+          <t>42704438</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13709,7 +13487,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>109동</t>
+          <t>114동</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13734,14 +13512,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>월세</t>
@@ -13754,17 +13532,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -13784,17 +13562,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>O인기동,전입가능O조건맞춰찾아드립니다입주일협의</t>
+          <t>O상시입주가능O조건부전입가능,꼭확인하세요</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -13810,7 +13588,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42556700</t>
+          <t>42615752</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13820,7 +13598,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>102동</t>
+          <t>115동</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13840,17 +13618,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -13865,7 +13643,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -13875,7 +13653,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -13884,25 +13662,25 @@
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>O전입불가O시스템에어컨4,초등학교가까운동</t>
+          <t>O전입XO보증금1억가능,빠른입주환영,역가까운로얄동</t>
         </is>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA7" t="n">
         <v>230</v>
@@ -13921,7 +13699,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42527493</t>
+          <t>42557757</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13931,32 +13709,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104동</t>
+          <t>109동</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>84.32</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>고</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -13976,7 +13754,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -13986,7 +13764,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -13996,32 +13774,24 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
+          <t>O인기동,전입가능O조건맞춰찾아드립니다입주일협의</t>
         </is>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AA8" t="n">
         <v>120</v>
@@ -14040,7 +13810,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42383838</t>
+          <t>42556700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14050,7 +13820,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>108동</t>
+          <t>102동</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -14070,12 +13840,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14095,17 +13865,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>230</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -14121,25 +13891,21 @@
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>O전입가능O풀옵션,시에4,냉장고,김치냉장고,워시타워등</t>
+          <t>O전입불가O시스템에어컨4,초등학교가까운동</t>
         </is>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="AA9" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -14155,7 +13921,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>42352823</t>
+          <t>42527493</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14165,17 +13931,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>123동</t>
+          <t>104동</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -14215,12 +13981,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -14229,11 +13995,7 @@
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
@@ -14245,10 +14007,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>O대출가능전입가능O가전옵션풀,시스템에어컨,장기거주환영</t>
+          <t>O전입O대출X채광좋은층O당일확인,중문,현관고급화</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -14258,7 +14024,7 @@
         <v>25000</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -14274,7 +14040,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>42232723</t>
+          <t>42383838</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -14284,7 +14050,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>101동</t>
+          <t>108동</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14304,12 +14070,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14324,22 +14090,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>116,830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -14353,31 +14119,27 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>O전입불가O입주일협의가능,막힘없이트인뷰,시에4</t>
+          <t>O전입가능O풀옵션,시에4,냉장고,김치냉장고,워시타워등</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>116830</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="AA11" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -14393,7 +14155,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42142455</t>
+          <t>42232723</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -14403,32 +14165,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>126동</t>
+          <t>101동</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>84.42</t>
+          <t>112.60</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>59.75</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14443,22 +14205,22 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116,830</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -14472,27 +14234,31 @@
           <t>O</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>O초역세권동,전입가능O에어컨4,붙박이장,냉장고3,워시타워</t>
+          <t>O전입불가O입주일협의가능,막힘없이트인뷰,시에4</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>116830</v>
       </c>
       <c r="Z12" t="n">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -14953,232 +14719,6 @@
       </c>
       <c r="AA16" t="n">
         <v>110</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>41926893</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>110동</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>129.28</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>101.73</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>O전월세는이강O귀한101타입,채광굿,입주일협의가능</t>
-        </is>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20261003</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>41951369</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>매교역팰루시드</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>112동</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>112.60</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>월세</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>팰루시드이강부동산공인중개사사무소</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>O조건맞춰드립니다O전입X,빠른입주환영,층간소음걱정없는1층</t>
-        </is>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>25000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
